--- a/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/0_fold/77.xlsx
+++ b/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/0_fold/77.xlsx
@@ -426,13 +426,13 @@
         <v>-21.61150275022093</v>
       </c>
       <c r="E2">
-        <v>-12.38020244189526</v>
+        <v>-10.98744761846621</v>
       </c>
       <c r="F2">
-        <v>-2.247559719219238</v>
+        <v>-1.81646075545432</v>
       </c>
       <c r="G2">
-        <v>-9.55822809492534</v>
+        <v>-7.898707895362862</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -449,13 +449,13 @@
         <v>-21.27706521001012</v>
       </c>
       <c r="E3">
-        <v>-11.98367114388762</v>
+        <v>-11.71357031170012</v>
       </c>
       <c r="F3">
-        <v>-2.053333242652241</v>
+        <v>-1.713821064043044</v>
       </c>
       <c r="G3">
-        <v>-8.884912790420671</v>
+        <v>-7.081079289710282</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -472,13 +472,13 @@
         <v>-20.94606219087643</v>
       </c>
       <c r="E4">
-        <v>-13.4018850481878</v>
+        <v>-11.79235217401156</v>
       </c>
       <c r="F4">
-        <v>-1.871248147108076</v>
+        <v>-1.635462477942628</v>
       </c>
       <c r="G4">
-        <v>-8.593422566233382</v>
+        <v>-7.385894459693137</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -495,13 +495,13 @@
         <v>-20.64984899473806</v>
       </c>
       <c r="E5">
-        <v>-13.68699324323671</v>
+        <v>-13.58894272402264</v>
       </c>
       <c r="F5">
-        <v>-2.025493470978955</v>
+        <v>-1.694661754383694</v>
       </c>
       <c r="G5">
-        <v>-8.746998773800172</v>
+        <v>-7.341844340747596</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -518,13 +518,13 @@
         <v>-20.38040008763267</v>
       </c>
       <c r="E6">
-        <v>-14.44577076253993</v>
+        <v>-12.78181468773952</v>
       </c>
       <c r="F6">
-        <v>-1.894381135198655</v>
+        <v>-1.656417688131247</v>
       </c>
       <c r="G6">
-        <v>-8.249009961055304</v>
+        <v>-6.564001871385976</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -541,13 +541,13 @@
         <v>-20.14824308604013</v>
       </c>
       <c r="E7">
-        <v>-14.98249003040303</v>
+        <v>-14.98875743842965</v>
       </c>
       <c r="F7">
-        <v>-1.843280806854759</v>
+        <v>-1.795658793235218</v>
       </c>
       <c r="G7">
-        <v>-7.756195530988316</v>
+        <v>-6.23706894665525</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -564,13 +564,13 @@
         <v>-19.92536077249484</v>
       </c>
       <c r="E8">
-        <v>-16.69025456275365</v>
+        <v>-14.47727082773729</v>
       </c>
       <c r="F8">
-        <v>-1.875479447801576</v>
+        <v>-1.727857749683482</v>
       </c>
       <c r="G8">
-        <v>-7.433430583091533</v>
+        <v>-6.330883186147117</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -587,13 +587,13 @@
         <v>-19.71965463504602</v>
       </c>
       <c r="E9">
-        <v>-16.87428268947736</v>
+        <v>-15.69191171149666</v>
       </c>
       <c r="F9">
-        <v>-2.104856038371565</v>
+        <v>-1.50422671541931</v>
       </c>
       <c r="G9">
-        <v>-7.329125224785716</v>
+        <v>-5.766441792792459</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -610,13 +610,13 @@
         <v>-19.50640297938629</v>
       </c>
       <c r="E10">
-        <v>-17.00170036263118</v>
+        <v>-16.22357267389319</v>
       </c>
       <c r="F10">
-        <v>-1.800521309889652</v>
+        <v>-1.397307678005173</v>
       </c>
       <c r="G10">
-        <v>-7.201877785892749</v>
+        <v>-5.7935981978511</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -633,13 +633,13 @@
         <v>-19.28165110506115</v>
       </c>
       <c r="E11">
-        <v>-18.21966967478619</v>
+        <v>-17.47169709446527</v>
       </c>
       <c r="F11">
-        <v>-1.666555248406707</v>
+        <v>-1.450256094024714</v>
       </c>
       <c r="G11">
-        <v>-6.746830059337767</v>
+        <v>-5.014007760444746</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -656,13 +656,13 @@
         <v>-19.04896879653056</v>
       </c>
       <c r="E12">
-        <v>-18.99616258440742</v>
+        <v>-17.77746418793718</v>
       </c>
       <c r="F12">
-        <v>-1.481288393668389</v>
+        <v>-1.448030270813392</v>
       </c>
       <c r="G12">
-        <v>-6.212047843469438</v>
+        <v>-4.105623859378586</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -679,13 +679,13 @@
         <v>-18.79722615846517</v>
       </c>
       <c r="E13">
-        <v>-20.30412626051685</v>
+        <v>-18.55402049619451</v>
       </c>
       <c r="F13">
-        <v>-1.4891032117464</v>
+        <v>-1.176526227606632</v>
       </c>
       <c r="G13">
-        <v>-5.21875838095759</v>
+        <v>-3.79554161144275</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -702,13 +702,13 @@
         <v>-18.55731181721774</v>
       </c>
       <c r="E14">
-        <v>-20.37543161224163</v>
+        <v>-19.2484846276408</v>
       </c>
       <c r="F14">
-        <v>-1.641849190618212</v>
+        <v>-0.9745835086825569</v>
       </c>
       <c r="G14">
-        <v>-5.539487343347722</v>
+        <v>-4.444547580052552</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -725,13 +725,13 @@
         <v>-18.3317666104772</v>
       </c>
       <c r="E15">
-        <v>-21.56272504146868</v>
+        <v>-20.882788254639</v>
       </c>
       <c r="F15">
-        <v>-1.273981167443785</v>
+        <v>-0.9721497652531319</v>
       </c>
       <c r="G15">
-        <v>-4.557718579312538</v>
+        <v>-3.322292505512855</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -748,13 +748,13 @@
         <v>-18.14214404669432</v>
       </c>
       <c r="E16">
-        <v>-22.65520581039713</v>
+        <v>-21.39611795425247</v>
       </c>
       <c r="F16">
-        <v>-0.9930950350329174</v>
+        <v>-0.673466159193117</v>
       </c>
       <c r="G16">
-        <v>-4.844828951751371</v>
+        <v>-2.427197134241329</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -771,13 +771,13 @@
         <v>-17.99866781926692</v>
       </c>
       <c r="E17">
-        <v>-23.77531027077237</v>
+        <v>-22.33862019252089</v>
       </c>
       <c r="F17">
-        <v>-0.9118553871055644</v>
+        <v>-0.6848744350644718</v>
       </c>
       <c r="G17">
-        <v>-4.933925663849775</v>
+        <v>-3.091348848693297</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -794,13 +794,13 @@
         <v>-17.88520112631549</v>
       </c>
       <c r="E18">
-        <v>-24.24605420081772</v>
+        <v>-23.51661666461019</v>
       </c>
       <c r="F18">
-        <v>-0.509605974877944</v>
+        <v>-0.2384357637345119</v>
       </c>
       <c r="G18">
-        <v>-4.274915226620296</v>
+        <v>-2.608519023972752</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -817,13 +817,13 @@
         <v>-17.80446010623962</v>
       </c>
       <c r="E19">
-        <v>-25.60888486800409</v>
+        <v>-24.05161964082438</v>
       </c>
       <c r="F19">
-        <v>-0.4066440485469794</v>
+        <v>0.1170108902349364</v>
       </c>
       <c r="G19">
-        <v>-4.047351636796334</v>
+        <v>-2.589880652586655</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -840,13 +840,13 @@
         <v>-17.7229429435376</v>
       </c>
       <c r="E20">
-        <v>-25.62819428117279</v>
+        <v>-25.1776156458836</v>
       </c>
       <c r="F20">
-        <v>-0.09007350515831479</v>
+        <v>0.3653471539202002</v>
       </c>
       <c r="G20">
-        <v>-3.989605790954827</v>
+        <v>-1.943927006964061</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -863,13 +863,13 @@
         <v>-17.62754304761912</v>
       </c>
       <c r="E21">
-        <v>-26.52438381576476</v>
+        <v>-24.96087835140249</v>
       </c>
       <c r="F21">
-        <v>0.06198989897359045</v>
+        <v>0.8257520996613599</v>
       </c>
       <c r="G21">
-        <v>-3.639234203806061</v>
+        <v>-2.876236220642534</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -886,13 +886,13 @@
         <v>-17.49921182126492</v>
       </c>
       <c r="E22">
-        <v>-27.38968915762442</v>
+        <v>-26.40197916333744</v>
       </c>
       <c r="F22">
-        <v>0.582439884274075</v>
+        <v>0.749461118598331</v>
       </c>
       <c r="G22">
-        <v>-4.195180737306949</v>
+        <v>-2.357202269904519</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -909,13 +909,13 @@
         <v>-17.31428724816843</v>
       </c>
       <c r="E23">
-        <v>-27.93955458553179</v>
+        <v>-26.02014729195869</v>
       </c>
       <c r="F23">
-        <v>0.7757833211896881</v>
+        <v>1.135503522590179</v>
       </c>
       <c r="G23">
-        <v>-4.146952709890847</v>
+        <v>-2.576012777322648</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -932,13 +932,13 @@
         <v>-17.07798903398073</v>
       </c>
       <c r="E24">
-        <v>-28.41520285292745</v>
+        <v>-27.21138502204641</v>
       </c>
       <c r="F24">
-        <v>0.8707871218819577</v>
+        <v>1.305083583821683</v>
       </c>
       <c r="G24">
-        <v>-4.168706304629398</v>
+        <v>-2.264139524250066</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -955,13 +955,13 @@
         <v>-16.77452078782092</v>
       </c>
       <c r="E25">
-        <v>-28.47839770770448</v>
+        <v>-27.94188674964574</v>
       </c>
       <c r="F25">
-        <v>0.7399150126484695</v>
+        <v>1.284008260359657</v>
       </c>
       <c r="G25">
-        <v>-4.203059835690415</v>
+        <v>-1.888574685547447</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -978,13 +978,13 @@
         <v>-16.41547272047698</v>
       </c>
       <c r="E26">
-        <v>-28.68999065571288</v>
+        <v>-26.6995723612255</v>
       </c>
       <c r="F26">
-        <v>0.9109032984647322</v>
+        <v>1.46803670583079</v>
       </c>
       <c r="G26">
-        <v>-4.576211286694907</v>
+        <v>-2.870654640863323</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1001,13 +1001,13 @@
         <v>-16.00354749022461</v>
       </c>
       <c r="E27">
-        <v>-28.90880651976352</v>
+        <v>-26.80119131795762</v>
       </c>
       <c r="F27">
-        <v>0.5893840882117433</v>
+        <v>1.165521900532827</v>
       </c>
       <c r="G27">
-        <v>-3.855197642060417</v>
+        <v>-2.453261059272012</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1024,13 +1024,13 @@
         <v>-15.53644764202361</v>
       </c>
       <c r="E28">
-        <v>-28.74490293152989</v>
+        <v>-26.42866998913864</v>
       </c>
       <c r="F28">
-        <v>0.6575620389317538</v>
+        <v>1.422867488090939</v>
       </c>
       <c r="G28">
-        <v>-4.259620506228863</v>
+        <v>-2.763776988673492</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1047,13 +1047,13 @@
         <v>-15.03162567515185</v>
       </c>
       <c r="E29">
-        <v>-28.4582731692144</v>
+        <v>-27.49143038315475</v>
       </c>
       <c r="F29">
-        <v>0.8001919950805783</v>
+        <v>1.281324349974587</v>
       </c>
       <c r="G29">
-        <v>-4.490941565239899</v>
+        <v>-2.178979050797854</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1070,13 +1070,13 @@
         <v>-14.48659815304099</v>
       </c>
       <c r="E30">
-        <v>-28.00801605557975</v>
+        <v>-26.29525208792466</v>
       </c>
       <c r="F30">
-        <v>0.8321040209060264</v>
+        <v>1.006342820410874</v>
       </c>
       <c r="G30">
-        <v>-4.250556232542339</v>
+        <v>-2.44386242048602</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1093,13 +1093,13 @@
         <v>-13.9221553988549</v>
       </c>
       <c r="E31">
-        <v>-28.47396433165098</v>
+        <v>-26.27934355873571</v>
       </c>
       <c r="F31">
-        <v>0.6761936785555203</v>
+        <v>1.146881977235033</v>
       </c>
       <c r="G31">
-        <v>-4.182630459167573</v>
+        <v>-2.56837203821801</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1116,13 +1116,13 @@
         <v>-13.34732697653483</v>
       </c>
       <c r="E32">
-        <v>-28.03471593832898</v>
+        <v>-26.52810622139907</v>
       </c>
       <c r="F32">
-        <v>0.5348443784114238</v>
+        <v>0.7952300743378092</v>
       </c>
       <c r="G32">
-        <v>-4.054710979530134</v>
+        <v>-2.023393342088726</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1139,13 +1139,13 @@
         <v>-12.76369115180644</v>
       </c>
       <c r="E33">
-        <v>-27.94899192536377</v>
+        <v>-25.76937851530993</v>
       </c>
       <c r="F33">
-        <v>0.2297740596758247</v>
+        <v>0.652239778368767</v>
       </c>
       <c r="G33">
-        <v>-3.869237665692466</v>
+        <v>-1.840512185408308</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1162,13 +1162,13 @@
         <v>-12.18133800818734</v>
       </c>
       <c r="E34">
-        <v>-26.61801454434736</v>
+        <v>-26.03122393938145</v>
       </c>
       <c r="F34">
-        <v>0.6132021361444375</v>
+        <v>0.7165434547458842</v>
       </c>
       <c r="G34">
-        <v>-2.965614329111777</v>
+        <v>-1.516181349471448</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1185,13 +1185,13 @@
         <v>-11.58899115413246</v>
       </c>
       <c r="E35">
-        <v>-26.84597792589348</v>
+        <v>-24.8689639144688</v>
       </c>
       <c r="F35">
-        <v>0.5021942772300814</v>
+        <v>0.6132054496140487</v>
       </c>
       <c r="G35">
-        <v>-4.154811945001077</v>
+        <v>-0.9357202262522564</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1208,13 +1208,13 @@
         <v>-11.00485059872213</v>
       </c>
       <c r="E36">
-        <v>-26.69850364135969</v>
+        <v>-25.27303512169922</v>
       </c>
       <c r="F36">
-        <v>0.2976446860893966</v>
+        <v>0.602623056043285</v>
       </c>
       <c r="G36">
-        <v>-3.263133056726079</v>
+        <v>-1.336627291057997</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1231,13 +1231,13 @@
         <v>-10.44278193520249</v>
       </c>
       <c r="E37">
-        <v>-26.40997644843498</v>
+        <v>-24.41656483262853</v>
       </c>
       <c r="F37">
-        <v>0.3075287659396003</v>
+        <v>0.6768033569639808</v>
       </c>
       <c r="G37">
-        <v>-2.909010621481319</v>
+        <v>-0.7450261820991575</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1254,13 +1254,13 @@
         <v>-9.919662925213586</v>
       </c>
       <c r="E38">
-        <v>-25.18816246184747</v>
+        <v>-24.07809309987322</v>
       </c>
       <c r="F38">
-        <v>0.2740618944990975</v>
+        <v>0.3426714246359666</v>
       </c>
       <c r="G38">
-        <v>-2.953908240084914</v>
+        <v>-1.10949407215414</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1277,13 +1277,13 @@
         <v>-9.458735615858235</v>
       </c>
       <c r="E39">
-        <v>-25.39943841667532</v>
+        <v>-23.43995412813434</v>
       </c>
       <c r="F39">
-        <v>0.09716486399866586</v>
+        <v>0.3965964858234087</v>
       </c>
       <c r="G39">
-        <v>-2.296205468343447</v>
+        <v>-0.3376304480364452</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1300,13 +1300,13 @@
         <v>-9.061341172794272</v>
       </c>
       <c r="E40">
-        <v>-24.68135829327904</v>
+        <v>-23.66763221581798</v>
       </c>
       <c r="F40">
-        <v>0.1259274369586703</v>
+        <v>0.2988209678013719</v>
       </c>
       <c r="G40">
-        <v>-2.600994153961988</v>
+        <v>-0.4947654920579521</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1323,13 +1323,13 @@
         <v>-8.747764493685025</v>
       </c>
       <c r="E41">
-        <v>-24.18565341450341</v>
+        <v>-22.90635045038852</v>
       </c>
       <c r="F41">
-        <v>0.01971748204132888</v>
+        <v>0.4094660017933019</v>
       </c>
       <c r="G41">
-        <v>-2.464960527207796</v>
+        <v>-0.138852051676446</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1346,13 +1346,13 @@
         <v>-8.517506047048977</v>
       </c>
       <c r="E42">
-        <v>-23.24242209191976</v>
+        <v>-22.39841869179218</v>
       </c>
       <c r="F42">
-        <v>0.06004737741402561</v>
+        <v>0.2494502705945214</v>
       </c>
       <c r="G42">
-        <v>-1.57836001579004</v>
+        <v>0.2489982215224091</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1369,13 +1369,13 @@
         <v>-8.373754022358153</v>
       </c>
       <c r="E43">
-        <v>-23.47183005667433</v>
+        <v>-21.56851243125048</v>
       </c>
       <c r="F43">
-        <v>0.1301835886742541</v>
+        <v>0.1866997830976532</v>
       </c>
       <c r="G43">
-        <v>-1.765521707852737</v>
+        <v>0.5562102264756967</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1392,13 +1392,13 @@
         <v>-8.320304352826692</v>
       </c>
       <c r="E44">
-        <v>-22.3555657422576</v>
+        <v>-21.54403150076501</v>
       </c>
       <c r="F44">
-        <v>0.1093128719607206</v>
+        <v>0.1696089068430938</v>
       </c>
       <c r="G44">
-        <v>-1.497410556263781</v>
+        <v>0.2972593543939045</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1415,13 +1415,13 @@
         <v>-8.345262445555505</v>
       </c>
       <c r="E45">
-        <v>-22.76786971523396</v>
+        <v>-21.27125434043898</v>
       </c>
       <c r="F45">
-        <v>0.2382134667755461</v>
+        <v>-0.04367250509050049</v>
       </c>
       <c r="G45">
-        <v>-1.681771526800254</v>
+        <v>0.3270509537018059</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1438,13 +1438,13 @@
         <v>-8.456192792767032</v>
       </c>
       <c r="E46">
-        <v>-22.32924625132501</v>
+        <v>-20.32897399739694</v>
       </c>
       <c r="F46">
-        <v>-0.2339004522041846</v>
+        <v>0.1803760263446818</v>
       </c>
       <c r="G46">
-        <v>-1.583358939554339</v>
+        <v>0.1985322653217592</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1461,13 +1461,13 @@
         <v>-8.638901421935106</v>
       </c>
       <c r="E47">
-        <v>-21.3640156020121</v>
+        <v>-19.95261252261946</v>
       </c>
       <c r="F47">
-        <v>-0.01690132736682607</v>
+        <v>-0.1553082664961787</v>
       </c>
       <c r="G47">
-        <v>-1.561360364445882</v>
+        <v>0.4399869042285032</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1484,13 +1484,13 @@
         <v>-8.890976772253794</v>
       </c>
       <c r="E48">
-        <v>-21.1690693244559</v>
+        <v>-20.09117024183215</v>
       </c>
       <c r="F48">
-        <v>-0.164111326885729</v>
+        <v>-0.004257127330494412</v>
       </c>
       <c r="G48">
-        <v>-1.868539263943777</v>
+        <v>0.1624175240338498</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1507,13 +1507,13 @@
         <v>-9.204727945126507</v>
       </c>
       <c r="E49">
-        <v>-20.66959222683188</v>
+        <v>-18.85342961215965</v>
       </c>
       <c r="F49">
-        <v>-0.3907253121673814</v>
+        <v>-0.04291869075395294</v>
       </c>
       <c r="G49">
-        <v>-2.231676314691973</v>
+        <v>0.7982210370330384</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -1530,13 +1530,13 @@
         <v>-9.562659226668666</v>
       </c>
       <c r="E50">
-        <v>-19.81407744577681</v>
+        <v>-19.49149612831442</v>
       </c>
       <c r="F50">
-        <v>-0.510605814333123</v>
+        <v>-0.4761962607882343</v>
       </c>
       <c r="G50">
-        <v>-1.87279662550728</v>
+        <v>-0.2291041441680571</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -1553,13 +1553,13 @@
         <v>-9.962128132592859</v>
       </c>
       <c r="E51">
-        <v>-19.15719512012017</v>
+        <v>-18.04022889223225</v>
       </c>
       <c r="F51">
-        <v>-0.611508419300728</v>
+        <v>-0.5178714248230775</v>
       </c>
       <c r="G51">
-        <v>-2.33602802063534</v>
+        <v>0.3619573458678813</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -1576,13 +1576,13 @@
         <v>-10.38107142681845</v>
       </c>
       <c r="E52">
-        <v>-19.0646376398774</v>
+        <v>-18.91630747375616</v>
       </c>
       <c r="F52">
-        <v>-0.4251398359166868</v>
+        <v>-0.08511572625255975</v>
       </c>
       <c r="G52">
-        <v>-2.502949037270933</v>
+        <v>-0.2080490745382924</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -1599,13 +1599,13 @@
         <v>-10.81665330330508</v>
       </c>
       <c r="E53">
-        <v>-18.10773485426459</v>
+        <v>-18.09275013377321</v>
       </c>
       <c r="F53">
-        <v>-0.3119044970562028</v>
+        <v>-0.2771652532849999</v>
       </c>
       <c r="G53">
-        <v>-2.053661659954283</v>
+        <v>-0.1966707295198173</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -1622,13 +1622,13 @@
         <v>-11.25854270455038</v>
       </c>
       <c r="E54">
-        <v>-17.26984036557336</v>
+        <v>-17.71503011679343</v>
       </c>
       <c r="F54">
-        <v>-0.5301834495308865</v>
+        <v>-0.2466705640857417</v>
       </c>
       <c r="G54">
-        <v>-2.605228341706716</v>
+        <v>-0.6818113150267742</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -1645,13 +1645,13 @@
         <v>-11.69634639863622</v>
       </c>
       <c r="E55">
-        <v>-17.92995602167147</v>
+        <v>-17.9105515105486</v>
       </c>
       <c r="F55">
-        <v>-0.4080829227256422</v>
+        <v>-0.141284006366783</v>
       </c>
       <c r="G55">
-        <v>-2.433520276221337</v>
+        <v>-0.7105501608531873</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -1668,13 +1668,13 @@
         <v>-12.13196700987891</v>
       </c>
       <c r="E56">
-        <v>-16.76208068898931</v>
+        <v>-16.84122482922137</v>
       </c>
       <c r="F56">
-        <v>-0.59328764990875</v>
+        <v>-0.3697982664704574</v>
       </c>
       <c r="G56">
-        <v>-3.415222829345737</v>
+        <v>-1.129940001404679</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -1691,13 +1691,13 @@
         <v>-12.5471320689691</v>
       </c>
       <c r="E57">
-        <v>-16.17725091326873</v>
+        <v>-16.00302693277163</v>
       </c>
       <c r="F57">
-        <v>-0.5540801923668467</v>
+        <v>-0.3889443222513624</v>
       </c>
       <c r="G57">
-        <v>-3.207452991301077</v>
+        <v>-0.6356523785727159</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -1714,13 +1714,13 @@
         <v>-12.94395192851594</v>
       </c>
       <c r="E58">
-        <v>-16.80526421712646</v>
+        <v>-15.92355221393701</v>
       </c>
       <c r="F58">
-        <v>-0.5850801856818125</v>
+        <v>-0.3929776431355932</v>
       </c>
       <c r="G58">
-        <v>-3.704624099297745</v>
+        <v>-1.497254960623435</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -1737,13 +1737,13 @@
         <v>-13.31122252633875</v>
       </c>
       <c r="E59">
-        <v>-16.4603846936503</v>
+        <v>-15.21725065143467</v>
       </c>
       <c r="F59">
-        <v>-0.6413114217186486</v>
+        <v>-0.4287407490166563</v>
       </c>
       <c r="G59">
-        <v>-4.181660469324566</v>
+        <v>-1.564889405990745</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -1760,13 +1760,13 @@
         <v>-13.63917094398807</v>
       </c>
       <c r="E60">
-        <v>-15.82042980383434</v>
+        <v>-15.45823339575285</v>
       </c>
       <c r="F60">
-        <v>-0.7393263379200945</v>
+        <v>-0.4125122032284111</v>
       </c>
       <c r="G60">
-        <v>-3.513625484955033</v>
+        <v>-1.900952815318782</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -1783,13 +1783,13 @@
         <v>-13.92864318682281</v>
       </c>
       <c r="E61">
-        <v>-15.29718274614406</v>
+        <v>-14.97814269535567</v>
       </c>
       <c r="F61">
-        <v>-0.799493147487631</v>
+        <v>-0.4528329865596771</v>
       </c>
       <c r="G61">
-        <v>-4.173364242203153</v>
+        <v>-2.006820751119135</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -1806,13 +1806,13 @@
         <v>-14.16357841713823</v>
       </c>
       <c r="E62">
-        <v>-14.96731058552932</v>
+        <v>-13.62798269844276</v>
       </c>
       <c r="F62">
-        <v>-0.8723488889312503</v>
+        <v>-0.5597702480566765</v>
       </c>
       <c r="G62">
-        <v>-4.662715841636063</v>
+        <v>-1.889773103032663</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -1829,13 +1829,13 @@
         <v>-14.35072748850122</v>
       </c>
       <c r="E63">
-        <v>-14.39633794027221</v>
+        <v>-13.97719597154426</v>
       </c>
       <c r="F63">
-        <v>-0.9071411482162324</v>
+        <v>-0.5155553095648501</v>
       </c>
       <c r="G63">
-        <v>-4.457402428381542</v>
+        <v>-1.6688438464694</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -1852,13 +1852,13 @@
         <v>-14.48348300370129</v>
       </c>
       <c r="E64">
-        <v>-13.85607740573511</v>
+        <v>-14.04985080852332</v>
       </c>
       <c r="F64">
-        <v>-0.8312312161584913</v>
+        <v>-0.6867887921323415</v>
       </c>
       <c r="G64">
-        <v>-4.924371429423439</v>
+        <v>-2.611193944768483</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -1875,13 +1875,13 @@
         <v>-14.56002291634318</v>
       </c>
       <c r="E65">
-        <v>-14.08330264601798</v>
+        <v>-13.28749579475404</v>
       </c>
       <c r="F65">
-        <v>-1.104282649673681</v>
+        <v>-0.8211367309879765</v>
       </c>
       <c r="G65">
-        <v>-5.291040832262038</v>
+        <v>-2.314214836077082</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -1898,13 +1898,13 @@
         <v>-14.58743681082246</v>
       </c>
       <c r="E66">
-        <v>-13.86566418520935</v>
+        <v>-13.77691968008103</v>
       </c>
       <c r="F66">
-        <v>-1.016744096015441</v>
+        <v>-0.5705133449035833</v>
       </c>
       <c r="G66">
-        <v>-4.747584987080819</v>
+        <v>-2.594502174159477</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -1921,13 +1921,13 @@
         <v>-14.55758771584077</v>
       </c>
       <c r="E67">
-        <v>-13.82961300363428</v>
+        <v>-13.84553511824525</v>
       </c>
       <c r="F67">
-        <v>-0.9939838732561214</v>
+        <v>-1.1778483019815</v>
       </c>
       <c r="G67">
-        <v>-4.799014312033396</v>
+        <v>-2.606277784642665</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -1944,13 +1944,13 @@
         <v>-14.48581445398852</v>
       </c>
       <c r="E68">
-        <v>-12.87793154855232</v>
+        <v>-13.99993343953677</v>
       </c>
       <c r="F68">
-        <v>-1.444385454241074</v>
+        <v>-1.121380152867463</v>
       </c>
       <c r="G68">
-        <v>-5.321785868685249</v>
+        <v>-2.429587348120683</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -1967,13 +1967,13 @@
         <v>-14.37342505782867</v>
       </c>
       <c r="E69">
-        <v>-12.76327964362612</v>
+        <v>-13.68648152567385</v>
       </c>
       <c r="F69">
-        <v>-1.318430533910604</v>
+        <v>-0.917744250972066</v>
       </c>
       <c r="G69">
-        <v>-4.867108923230665</v>
+        <v>-2.568060846937319</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -1990,13 +1990,13 @@
         <v>-14.22819623790159</v>
       </c>
       <c r="E70">
-        <v>-13.38123973518683</v>
+        <v>-13.20360581376195</v>
       </c>
       <c r="F70">
-        <v>-1.13565623668731</v>
+        <v>-1.154996958807872</v>
       </c>
       <c r="G70">
-        <v>-4.878758732983361</v>
+        <v>-2.564674158850644</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -2013,13 +2013,13 @@
         <v>-14.06562971797364</v>
       </c>
       <c r="E71">
-        <v>-13.02881577401389</v>
+        <v>-13.30916001440674</v>
       </c>
       <c r="F71">
-        <v>-1.62394982777852</v>
+        <v>-1.156918771182367</v>
       </c>
       <c r="G71">
-        <v>-5.002295050326804</v>
+        <v>-2.94520812640771</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -2036,13 +2036,13 @@
         <v>-13.88425559491837</v>
       </c>
       <c r="E72">
-        <v>-12.9312316876226</v>
+        <v>-13.42876154142332</v>
       </c>
       <c r="F72">
-        <v>-1.512361283314801</v>
+        <v>-1.269078060786615</v>
       </c>
       <c r="G72">
-        <v>-4.194127983825462</v>
+        <v>-2.440737265496948</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -2059,13 +2059,13 @@
         <v>-13.7061325980752</v>
       </c>
       <c r="E73">
-        <v>-12.86542843181714</v>
+        <v>-12.67616538914057</v>
       </c>
       <c r="F73">
-        <v>-1.459175954218059</v>
+        <v>-1.234149120880171</v>
       </c>
       <c r="G73">
-        <v>-4.518577999401734</v>
+        <v>-2.596428911663333</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -2082,13 +2082,13 @@
         <v>-13.53394824499214</v>
       </c>
       <c r="E74">
-        <v>-14.03669106305703</v>
+        <v>-13.17549304712233</v>
       </c>
       <c r="F74">
-        <v>-1.472366876740239</v>
+        <v>-1.556985435303611</v>
       </c>
       <c r="G74">
-        <v>-4.883337217464173</v>
+        <v>-2.70123747289112</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -2105,13 +2105,13 @@
         <v>-13.37710835546379</v>
       </c>
       <c r="E75">
-        <v>-14.31554543550136</v>
+        <v>-13.95103497720195</v>
       </c>
       <c r="F75">
-        <v>-1.552827030941557</v>
+        <v>-1.471332245854142</v>
       </c>
       <c r="G75">
-        <v>-4.387755171326354</v>
+        <v>-1.833632871777702</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -2128,13 +2128,13 @@
         <v>-13.24642631901072</v>
       </c>
       <c r="E76">
-        <v>-14.30255777204736</v>
+        <v>-13.69368632782005</v>
       </c>
       <c r="F76">
-        <v>-2.051475214567762</v>
+        <v>-1.697612399072466</v>
       </c>
       <c r="G76">
-        <v>-4.218314829535377</v>
+        <v>-2.325434274909672</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -2151,13 +2151,13 @@
         <v>-13.13319778875952</v>
       </c>
       <c r="E77">
-        <v>-13.62899254814647</v>
+        <v>-14.25351439854429</v>
       </c>
       <c r="F77">
-        <v>-1.657900465782258</v>
+        <v>-1.637717294013048</v>
       </c>
       <c r="G77">
-        <v>-3.652790887789376</v>
+        <v>-2.416421308511002</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -2174,13 +2174,13 @@
         <v>-13.05143617065605</v>
       </c>
       <c r="E78">
-        <v>-14.05025837118401</v>
+        <v>-14.21299361312366</v>
       </c>
       <c r="F78">
-        <v>-1.821324928843558</v>
+        <v>-1.867344879906085</v>
       </c>
       <c r="G78">
-        <v>-3.613193452594154</v>
+        <v>-1.565319776910851</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -2197,13 +2197,13 @@
         <v>-12.99205565516751</v>
       </c>
       <c r="E79">
-        <v>-15.07016128719153</v>
+        <v>-15.58239962456916</v>
       </c>
       <c r="F79">
-        <v>-1.899990010883011</v>
+        <v>-1.882674647062293</v>
       </c>
       <c r="G79">
-        <v>-3.773791327249738</v>
+        <v>-1.867413678460425</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -2220,13 +2220,13 @@
         <v>-12.95855803213879</v>
       </c>
       <c r="E80">
-        <v>-15.50801943899318</v>
+        <v>-15.25831032526222</v>
       </c>
       <c r="F80">
-        <v>-2.220323827382594</v>
+        <v>-2.000172764577583</v>
       </c>
       <c r="G80">
-        <v>-3.988778154570009</v>
+        <v>-1.924348440644811</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -2243,13 +2243,13 @@
         <v>-12.95367519049753</v>
       </c>
       <c r="E81">
-        <v>-15.99859808519212</v>
+        <v>-15.51403778094937</v>
       </c>
       <c r="F81">
-        <v>-2.151428510491758</v>
+        <v>-2.115667889712904</v>
       </c>
       <c r="G81">
-        <v>-3.312890556181325</v>
+        <v>-1.584782474136226</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -2266,13 +2266,13 @@
         <v>-12.96669790617634</v>
       </c>
       <c r="E82">
-        <v>-16.65577929013326</v>
+        <v>-16.49289460855137</v>
       </c>
       <c r="F82">
-        <v>-2.275563507638279</v>
+        <v>-2.325068400364382</v>
       </c>
       <c r="G82">
-        <v>-3.53853402959251</v>
+        <v>-1.300853535960633</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -2289,13 +2289,13 @@
         <v>-13.01023664170413</v>
       </c>
       <c r="E83">
-        <v>-17.12483409937375</v>
+        <v>-17.95922354918304</v>
       </c>
       <c r="F83">
-        <v>-2.346843694281773</v>
+        <v>-2.148270773952287</v>
       </c>
       <c r="G83">
-        <v>-3.208737482970314</v>
+        <v>-0.8480636014634338</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -2312,13 +2312,13 @@
         <v>-13.07169397016776</v>
       </c>
       <c r="E84">
-        <v>-18.30413477197726</v>
+        <v>-17.82454220372092</v>
       </c>
       <c r="F84">
-        <v>-2.574102977770206</v>
+        <v>-2.372557875199476</v>
       </c>
       <c r="G84">
-        <v>-2.64468342344375</v>
+        <v>-0.9541500332693791</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -2335,13 +2335,13 @@
         <v>-13.15558553944877</v>
       </c>
       <c r="E85">
-        <v>-18.97110653772298</v>
+        <v>-18.74427074620476</v>
       </c>
       <c r="F85">
-        <v>-2.4736733705896</v>
+        <v>-2.651315103385148</v>
       </c>
       <c r="G85">
-        <v>-2.522792447233324</v>
+        <v>-1.014229813716073</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -2358,13 +2358,13 @@
         <v>-13.25963188210535</v>
       </c>
       <c r="E86">
-        <v>-20.17114309280761</v>
+        <v>-20.71890278030141</v>
       </c>
       <c r="F86">
-        <v>-2.739452566675613</v>
+        <v>-2.62340077864561</v>
       </c>
       <c r="G86">
-        <v>-2.562264081698054</v>
+        <v>-0.6831587070612575</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -2381,13 +2381,13 @@
         <v>-13.37448571247017</v>
       </c>
       <c r="E87">
-        <v>-21.59175255985785</v>
+        <v>-20.97957080113093</v>
       </c>
       <c r="F87">
-        <v>-2.701403995130226</v>
+        <v>-2.609938979982716</v>
       </c>
       <c r="G87">
-        <v>-2.116932806300834</v>
+        <v>-0.3753077668188906</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -2404,13 +2404,13 @@
         <v>-13.51161196249471</v>
       </c>
       <c r="E88">
-        <v>-23.06210731388234</v>
+        <v>-21.76068728271398</v>
       </c>
       <c r="F88">
-        <v>-2.817464895201659</v>
+        <v>-2.808332972953197</v>
       </c>
       <c r="G88">
-        <v>-2.564200750838528</v>
+        <v>-0.6477458014276737</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -2427,13 +2427,13 @@
         <v>-13.65937327625633</v>
       </c>
       <c r="E89">
-        <v>-24.24047964931427</v>
+        <v>-23.70297695544785</v>
       </c>
       <c r="F89">
-        <v>-2.825334385528254</v>
+        <v>-2.784109853360534</v>
       </c>
       <c r="G89">
-        <v>-2.199358769137608</v>
+        <v>-0.7792208069742895</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -2450,13 +2450,13 @@
         <v>-13.83155648224912</v>
       </c>
       <c r="E90">
-        <v>-26.09310100822226</v>
+        <v>-25.84831434573763</v>
       </c>
       <c r="F90">
-        <v>-3.328106182085595</v>
+        <v>-2.907766054148236</v>
       </c>
       <c r="G90">
-        <v>-2.005913661641375</v>
+        <v>-0.4231583920435163</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -2473,13 +2473,13 @@
         <v>-14.03007828413286</v>
       </c>
       <c r="E91">
-        <v>-26.68200641054975</v>
+        <v>-27.27745092934432</v>
       </c>
       <c r="F91">
-        <v>-3.23929691283146</v>
+        <v>-3.086531881509383</v>
       </c>
       <c r="G91">
-        <v>-2.637284354163479</v>
+        <v>-0.8380028535695888</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -2496,13 +2496,13 @@
         <v>-14.25541690776211</v>
       </c>
       <c r="E92">
-        <v>-28.64127786081237</v>
+        <v>-28.58934984936642</v>
       </c>
       <c r="F92">
-        <v>-3.245965270423996</v>
+        <v>-3.087964128748824</v>
       </c>
       <c r="G92">
-        <v>-1.903922374667508</v>
+        <v>-0.3128410830383825</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -2519,13 +2519,13 @@
         <v>-14.52256339072517</v>
       </c>
       <c r="E93">
-        <v>-30.3449735592671</v>
+        <v>-30.65528724064271</v>
       </c>
       <c r="F93">
-        <v>-3.152274432065163</v>
+        <v>-3.435195034817306</v>
       </c>
       <c r="G93">
-        <v>-3.404701915621933</v>
+        <v>-1.05562156459358</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -2542,13 +2542,13 @@
         <v>-14.81828565019038</v>
       </c>
       <c r="E94">
-        <v>-32.83090427238479</v>
+        <v>-32.41331557024147</v>
       </c>
       <c r="F94">
-        <v>-3.199034943585792</v>
+        <v>-3.046749536989937</v>
       </c>
       <c r="G94">
-        <v>-3.10432618720724</v>
+        <v>-0.9679384554404435</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -2565,13 +2565,13 @@
         <v>-15.15229393514415</v>
       </c>
       <c r="E95">
-        <v>-34.9868835765926</v>
+        <v>-34.89845832888182</v>
       </c>
       <c r="F95">
-        <v>-3.238077556014539</v>
+        <v>-3.202979629157924</v>
       </c>
       <c r="G95">
-        <v>-3.759698334889061</v>
+        <v>-1.599322390144705</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -2588,13 +2588,13 @@
         <v>-15.51343538464189</v>
       </c>
       <c r="E96">
-        <v>-36.76331788879553</v>
+        <v>-36.76238728738696</v>
       </c>
       <c r="F96">
-        <v>-3.40847935770962</v>
+        <v>-3.53964802247331</v>
       </c>
       <c r="G96">
-        <v>-3.305137258528352</v>
+        <v>-1.833073389581565</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -2611,13 +2611,13 @@
         <v>-15.88544020175277</v>
       </c>
       <c r="E97">
-        <v>-39.39826030337262</v>
+        <v>-39.0003885770587</v>
       </c>
       <c r="F97">
-        <v>-3.109437896931595</v>
+        <v>-3.304436411918001</v>
       </c>
       <c r="G97">
-        <v>-3.81811622147504</v>
+        <v>-2.128311151319309</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -2634,13 +2634,13 @@
         <v>-16.2678656615796</v>
       </c>
       <c r="E98">
-        <v>-42.60901177344701</v>
+        <v>-40.60539976993828</v>
       </c>
       <c r="F98">
-        <v>-3.207199332707785</v>
+        <v>-3.250373841741695</v>
       </c>
       <c r="G98">
-        <v>-4.030219563630606</v>
+        <v>-3.060964661733866</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -2657,13 +2657,13 @@
         <v>-16.62379333131562</v>
       </c>
       <c r="E99">
-        <v>-44.86554131452113</v>
+        <v>-43.79058574000236</v>
       </c>
       <c r="F99">
-        <v>-3.182396355933162</v>
+        <v>-3.516850523180865</v>
       </c>
       <c r="G99">
-        <v>-4.637366994441863</v>
+        <v>-2.633083271874144</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -2680,13 +2680,13 @@
         <v>-16.96206861128946</v>
       </c>
       <c r="E100">
-        <v>-46.81935821784152</v>
+        <v>-46.71702149797918</v>
       </c>
       <c r="F100">
-        <v>-2.847342450685832</v>
+        <v>-3.303772061260956</v>
       </c>
       <c r="G100">
-        <v>-4.954298761098451</v>
+        <v>-2.967772804803382</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -2703,13 +2703,13 @@
         <v>-17.24265256647855</v>
       </c>
       <c r="E101">
-        <v>-49.77136060794714</v>
+        <v>-49.34648672324398</v>
       </c>
       <c r="F101">
-        <v>-2.997683678987316</v>
+        <v>-3.230897267367073</v>
       </c>
       <c r="G101">
-        <v>-5.308927709810719</v>
+        <v>-3.275286069400744</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -2726,13 +2726,13 @@
         <v>-17.48446848864388</v>
       </c>
       <c r="E102">
-        <v>-51.92112571369793</v>
+        <v>-50.41784895363767</v>
       </c>
       <c r="F102">
-        <v>-3.002745003818422</v>
+        <v>-3.433962424121941</v>
       </c>
       <c r="G102">
-        <v>-5.520382185040588</v>
+        <v>-2.985418012527698</v>
       </c>
     </row>
   </sheetData>
